--- a/data/classifiers/effects_severity.xlsx
+++ b/data/classifiers/effects_severity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elysetanzer/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiran/Documents/GitHub/citizen-scn2a/data/classifiers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B64B44-4A1A-A440-A2EA-95FD7BEBE329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A26E9A-759A-4044-9D10-B39F6B97D249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,207 +20,183 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
+  <si>
+    <t>adverse_effect</t>
+  </si>
+  <si>
+    <t>severity_score</t>
+  </si>
   <si>
     <t>Increased seizure frequency</t>
   </si>
   <si>
+    <t>Feeling agitated</t>
+  </si>
+  <si>
+    <t>Vomiting</t>
+  </si>
+  <si>
+    <t>Shortness of breath (dyspnea)</t>
+  </si>
+  <si>
+    <t>Change in behavior</t>
+  </si>
+  <si>
+    <t>Sedated</t>
+  </si>
+  <si>
+    <t>Insomnia</t>
+  </si>
+  <si>
+    <t>Drowsy</t>
+  </si>
+  <si>
+    <t>Treatment not tolerated</t>
+  </si>
+  <si>
+    <t>Irritability</t>
+  </si>
+  <si>
+    <t>Feeling aggressive</t>
+  </si>
+  <si>
+    <t>Rash</t>
+  </si>
+  <si>
+    <t>Acidosis</t>
+  </si>
+  <si>
+    <t>Ataxia</t>
+  </si>
+  <si>
+    <t>Lethargy</t>
+  </si>
+  <si>
+    <t>Syndrome of inappropriate antidiuretic hormone secretion (SIADH)</t>
+  </si>
+  <si>
+    <t>Nausea</t>
+  </si>
+  <si>
+    <t>Increased appetite</t>
+  </si>
+  <si>
+    <t>Disturbance in mood</t>
+  </si>
+  <si>
+    <t>Loss of appetite</t>
+  </si>
+  <si>
+    <t>Altered mental status</t>
+  </si>
+  <si>
+    <t>Constipation</t>
+  </si>
+  <si>
+    <t>Weight gain</t>
+  </si>
+  <si>
+    <t>Tremor</t>
+  </si>
+  <si>
+    <t>Poor balance</t>
+  </si>
+  <si>
+    <t>Unsteady gait</t>
+  </si>
+  <si>
+    <t>Elevated liver enzymes (Transaminitis)</t>
+  </si>
+  <si>
     <t>Developmental regression</t>
   </si>
   <si>
-    <t>Poor balance</t>
-  </si>
-  <si>
-    <t>Change in behavior</t>
-  </si>
-  <si>
-    <t>Feeding problem</t>
+    <t>Weight loss</t>
   </si>
   <si>
     <t>Fatigue</t>
   </si>
   <si>
-    <t>Constipation</t>
-  </si>
-  <si>
-    <t>Anxiety</t>
-  </si>
-  <si>
     <t>Low blood pressure (hypotension)</t>
   </si>
   <si>
-    <t>Loss of appetite</t>
-  </si>
-  <si>
-    <t>Sedated</t>
-  </si>
-  <si>
-    <t>Treatment not tolerated</t>
-  </si>
-  <si>
-    <t>Rash</t>
-  </si>
-  <si>
-    <t>Headache</t>
-  </si>
-  <si>
-    <t>Lethargy</t>
-  </si>
-  <si>
-    <t>Elevated liver enzymes (Transaminitis)</t>
-  </si>
-  <si>
-    <t>Vomiting</t>
-  </si>
-  <si>
-    <t>Nausea</t>
-  </si>
-  <si>
-    <t>Irritability</t>
-  </si>
-  <si>
     <t>Encephalopathy</t>
   </si>
   <si>
-    <t>Syndrome of inappropriate antidiuretic hormone secretion (SIADH)</t>
-  </si>
-  <si>
     <t>Drug-induced hyponatremia</t>
   </si>
   <si>
     <t>Dystonia</t>
   </si>
   <si>
-    <t>Dizziness</t>
-  </si>
-  <si>
-    <t>Unsteady gait</t>
-  </si>
-  <si>
     <t>Diarrhea</t>
   </si>
   <si>
-    <t>Drowsy</t>
-  </si>
-  <si>
-    <t>Hypertrophy of gingiva</t>
-  </si>
-  <si>
     <t>Medication not effective</t>
   </si>
   <si>
-    <t>Changes in mood</t>
-  </si>
-  <si>
-    <t>Acidosis</t>
-  </si>
-  <si>
-    <t>Chorea</t>
-  </si>
-  <si>
-    <t>Insomnia</t>
-  </si>
-  <si>
-    <t>Feeling agitated</t>
-  </si>
-  <si>
     <t>Blurring of visual image</t>
   </si>
   <si>
-    <t>Tremor</t>
-  </si>
-  <si>
     <t>Loss of hair (alopecia)</t>
   </si>
   <si>
-    <t>Increased appetite</t>
-  </si>
-  <si>
-    <t>Gastroparesis</t>
-  </si>
-  <si>
-    <t>Weight loss</t>
-  </si>
-  <si>
-    <t>Disturbance in mood</t>
-  </si>
-  <si>
-    <t>Feeling aggressive</t>
-  </si>
-  <si>
-    <t>Suicidal thoughts</t>
-  </si>
-  <si>
-    <t>Itching of skin</t>
-  </si>
-  <si>
-    <t>Disorder of lung</t>
-  </si>
-  <si>
-    <t>Shortness of breath (dyspnea)</t>
-  </si>
-  <si>
-    <t>Neutropenia</t>
-  </si>
-  <si>
     <t>Toxicity</t>
   </si>
   <si>
     <t>Sialorrhea</t>
   </si>
   <si>
-    <t>Thrombocytopenia</t>
-  </si>
-  <si>
-    <t>Dyskinesia</t>
-  </si>
-  <si>
-    <t>Impaired cognition (brain fog)</t>
-  </si>
-  <si>
     <t>Abnormal spontaneous eye movements</t>
   </si>
   <si>
-    <t>Dysphagia</t>
-  </si>
-  <si>
-    <t>Hypotonia</t>
-  </si>
-  <si>
-    <t>Nephrolithiasis</t>
-  </si>
-  <si>
-    <t>Cardiac arrhythmia</t>
-  </si>
-  <si>
     <t>Iatrogenic adrenal insufficiency</t>
   </si>
   <si>
-    <t>Ataxia</t>
-  </si>
-  <si>
     <t>Pancreatitis</t>
   </si>
   <si>
     <t>Abdominal discomfort</t>
   </si>
   <si>
-    <t>Weight gain</t>
-  </si>
-  <si>
     <t>Hyperammonemia</t>
   </si>
   <si>
-    <t>Altered mental status</t>
-  </si>
-  <si>
-    <t>Drug-induced hepatitis</t>
-  </si>
-  <si>
-    <t>adverse_effect</t>
-  </si>
-  <si>
-    <t>severity_score</t>
+    <t>Allergic reaction to drug</t>
+  </si>
+  <si>
+    <t>Bone pain</t>
+  </si>
+  <si>
+    <t>Dehydration</t>
+  </si>
+  <si>
+    <t>Disorder of autonomic nervous system</t>
+  </si>
+  <si>
+    <t>Drug-induced immune thrombocytopenia</t>
+  </si>
+  <si>
+    <t>Enlarged Liver (Hepatomegaly)</t>
+  </si>
+  <si>
+    <t>Epigastric discomfort</t>
+  </si>
+  <si>
+    <t>Gastrointestinal hemorrhage</t>
+  </si>
+  <si>
+    <t>Hypertension</t>
+  </si>
+  <si>
+    <t>Myoclonus</t>
+  </si>
+  <si>
+    <t>Retention of urine</t>
+  </si>
+  <si>
+    <t>Swelling (Edema)</t>
   </si>
   <si>
     <t>Severe</t>
@@ -236,7 +212,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,16 +228,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,24 +238,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -295,24 +251,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,539 +580,475 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="50.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>69</v>
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>69</v>
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>68</v>
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>67</v>
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>69</v>
+      <c r="B11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>69</v>
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>69</v>
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>69</v>
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>69</v>
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>68</v>
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>69</v>
+      <c r="B20" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>68</v>
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>68</v>
+      <c r="B23" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>69</v>
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>69</v>
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>69</v>
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>68</v>
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>68</v>
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>69</v>
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>68</v>
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>69</v>
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>67</v>
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>69</v>
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>67</v>
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>69</v>
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>68</v>
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>68</v>
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>68</v>
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>69</v>
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>68</v>
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>69</v>
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>69</v>
+      <c r="A47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>69</v>
+      <c r="A48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>69</v>
+      <c r="A49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>68</v>
+      <c r="A50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>69</v>
+      <c r="A51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>47</v>
+      <c r="A52" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>68</v>
+      <c r="A53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>69</v>
+      <c r="A54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>69</v>
+      <c r="A55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>68</v>
+      <c r="A56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>69</v>
+      <c r="A57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>62</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>67</v>
+      <c r="A58" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
